--- a/รายได้-PSD99-20220228-20220306.xlsx
+++ b/รายได้-PSD99-20220228-20220306.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="416">
   <si>
     <t>มาสเตอร์</t>
   </si>
@@ -1236,12 +1236,6 @@
   </si>
   <si>
     <t>ufruu9915</t>
-  </si>
-  <si>
-    <t>ufruu168</t>
-  </si>
-  <si>
-    <t>ufruu16899</t>
   </si>
   <si>
     <t>ยูสมาสเตอร์</t>
@@ -1305,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R339"/>
+  <dimension ref="A1:R338"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -20234,62 +20228,6 @@
       </c>
       <c r="R338" s="0" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="339" spans="1:18">
-      <c r="A339" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="B339" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="C339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D339" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="E339" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F339" s="0" t="n">
-        <v>2238</v>
-      </c>
-      <c r="G339" s="0" t="n">
-        <v>2239</v>
-      </c>
-      <c r="H339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M339" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N339" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O339" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P339" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q339" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="R339" s="0" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -20299,33 +20237,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>411</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="E1" s="0" t="s">
         <v>412</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="F1" s="0" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="G1" s="0" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="H1" s="0" t="s">
         <v>415</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -21651,32 +21589,6 @@
         <v>0</v>
       </c>
       <c r="H52" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="B53" s="0" t="n">
-        <v>-1785</v>
-      </c>
-      <c r="C53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/รายได้-PSD99-20220228-20220306.xlsx
+++ b/รายได้-PSD99-20220228-20220306.xlsx
@@ -2457,16 +2457,16 @@
         <v>4682</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="M21" s="0" t="n">
-        <v>5082</v>
+        <v>582</v>
       </c>
       <c r="N21" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>5082</v>
+        <v>582</v>
       </c>
       <c r="P21" s="0" t="s">
         <v>20</v>
@@ -2961,16 +2961,16 @@
         <v>212</v>
       </c>
       <c r="L30" s="0" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="M30" s="0" t="n">
-        <v>212</v>
+        <v>-811</v>
       </c>
       <c r="N30" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="0" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="P30" s="0" t="s">
         <v>20</v>
@@ -3745,16 +3745,16 @@
         <v>-1554</v>
       </c>
       <c r="L44" s="0" t="n">
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="M44" s="0" t="n">
-        <v>320</v>
+        <v>-1155</v>
       </c>
       <c r="N44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="0" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="P44" s="0" t="s">
         <v>20</v>
@@ -15729,16 +15729,16 @@
         <v>-18514</v>
       </c>
       <c r="L258" s="0" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M258" s="0" t="n">
-        <v>876</v>
+        <v>771</v>
       </c>
       <c r="N258" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O258" s="0" t="n">
-        <v>876</v>
+        <v>771</v>
       </c>
       <c r="P258" s="0" t="s">
         <v>20</v>
